--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.80357</v>
+        <v>17.08507</v>
       </c>
       <c r="D2" t="n">
-        <v>16.54792</v>
+        <v>16.53834</v>
       </c>
       <c r="E2" t="n">
-        <v>16.73651</v>
+        <v>16.99472</v>
       </c>
       <c r="F2" t="n">
-        <v>42.4699</v>
+        <v>42.00126</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05139</v>
+        <v>0.05062</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84163</v>
+        <v>1.87066</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.77661</v>
+        <v>16.80895</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69492</v>
+        <v>16.44531</v>
       </c>
       <c r="E3" t="n">
-        <v>16.83253</v>
+        <v>16.53696</v>
       </c>
       <c r="F3" t="n">
-        <v>42.89992</v>
+        <v>42.56234</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05108</v>
+        <v>0.05031</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82262</v>
+        <v>1.82578</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.89938</v>
+        <v>17.02365</v>
       </c>
       <c r="D4" t="n">
-        <v>16.56059</v>
+        <v>16.522</v>
       </c>
       <c r="E4" t="n">
-        <v>16.87451</v>
+        <v>16.89525</v>
       </c>
       <c r="F4" t="n">
-        <v>42.82522</v>
+        <v>42.55767</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05109</v>
+        <v>0.04972</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82835</v>
+        <v>1.81357</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.63881</v>
+        <v>16.86855</v>
       </c>
       <c r="D5" t="n">
-        <v>16.77146</v>
+        <v>16.50278</v>
       </c>
       <c r="E5" t="n">
-        <v>16.6353</v>
+        <v>16.57088</v>
       </c>
       <c r="F5" t="n">
-        <v>43.47899</v>
+        <v>42.66751</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05083</v>
+        <v>0.0517</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82241</v>
+        <v>1.82873</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.89837</v>
+        <v>16.92453</v>
       </c>
       <c r="D6" t="n">
-        <v>16.88493</v>
+        <v>16.8217</v>
       </c>
       <c r="E6" t="n">
-        <v>16.45827</v>
+        <v>16.86694</v>
       </c>
       <c r="F6" t="n">
-        <v>42.65285</v>
+        <v>42.10691</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05024</v>
+        <v>0.05036</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84148</v>
+        <v>1.82877</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.03731</v>
+        <v>17.02562</v>
       </c>
       <c r="D7" t="n">
-        <v>16.86964</v>
+        <v>16.63173</v>
       </c>
       <c r="E7" t="n">
-        <v>16.99783</v>
+        <v>16.82161</v>
       </c>
       <c r="F7" t="n">
-        <v>42.83966</v>
+        <v>42.18646</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05284</v>
+        <v>0.05053</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8242</v>
+        <v>1.83417</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.88745</v>
+        <v>17.02064</v>
       </c>
       <c r="D8" t="n">
-        <v>16.94964</v>
+        <v>16.5425</v>
       </c>
       <c r="E8" t="n">
-        <v>16.62958</v>
+        <v>16.61367</v>
       </c>
       <c r="F8" t="n">
-        <v>42.92304</v>
+        <v>42.80113</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05087</v>
+        <v>0.05082</v>
       </c>
       <c r="H8" t="n">
-        <v>1.88453</v>
+        <v>1.83385</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.93221</v>
+        <v>17.00005</v>
       </c>
       <c r="D9" t="n">
-        <v>16.41333</v>
+        <v>16.75659</v>
       </c>
       <c r="E9" t="n">
-        <v>16.9335</v>
+        <v>16.77711</v>
       </c>
       <c r="F9" t="n">
-        <v>43.01398</v>
+        <v>42.89632</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04946</v>
+        <v>0.05047</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79798</v>
+        <v>1.79403</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.02797</v>
+        <v>16.91494</v>
       </c>
       <c r="D10" t="n">
-        <v>16.47671</v>
+        <v>16.63552</v>
       </c>
       <c r="E10" t="n">
-        <v>16.69219</v>
+        <v>16.88257</v>
       </c>
       <c r="F10" t="n">
-        <v>40.94031</v>
+        <v>42.57488</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05049</v>
+        <v>0.05057</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83219</v>
+        <v>1.7954</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.96949</v>
+        <v>16.9297</v>
       </c>
       <c r="D12" t="n">
-        <v>16.49875</v>
+        <v>16.3994</v>
       </c>
       <c r="E12" t="n">
-        <v>16.42038</v>
+        <v>16.7017</v>
       </c>
       <c r="F12" t="n">
-        <v>43.21884</v>
+        <v>42.53676</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05156</v>
+        <v>0.05218</v>
       </c>
       <c r="H12" t="n">
-        <v>1.85108</v>
+        <v>1.84707</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.54943</v>
+        <v>17.19264</v>
       </c>
       <c r="D13" t="n">
-        <v>16.97444</v>
+        <v>16.68433</v>
       </c>
       <c r="E13" t="n">
-        <v>17.05545</v>
+        <v>16.78028</v>
       </c>
       <c r="F13" t="n">
-        <v>43.34101</v>
+        <v>42.82426</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05085</v>
+        <v>0.0504</v>
       </c>
       <c r="H13" t="n">
-        <v>1.81935</v>
+        <v>1.80191</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.60629</v>
+        <v>16.83365</v>
       </c>
       <c r="D14" t="n">
-        <v>16.62434</v>
+        <v>16.48378</v>
       </c>
       <c r="E14" t="n">
-        <v>16.86292</v>
+        <v>16.59139</v>
       </c>
       <c r="F14" t="n">
-        <v>42.09082</v>
+        <v>42.0463</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05053</v>
+        <v>0.05131</v>
       </c>
       <c r="H14" t="n">
-        <v>1.82916</v>
+        <v>1.84668</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.15882</v>
+        <v>16.98944</v>
       </c>
       <c r="D15" t="n">
-        <v>16.71245</v>
+        <v>16.72759</v>
       </c>
       <c r="E15" t="n">
-        <v>17.24629</v>
+        <v>16.92714</v>
       </c>
       <c r="F15" t="n">
-        <v>41.72197</v>
+        <v>43.22573</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05012</v>
+        <v>0.0504</v>
       </c>
       <c r="H15" t="n">
-        <v>1.86088</v>
+        <v>1.86422</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.98709</v>
+        <v>16.97352</v>
       </c>
       <c r="D16" t="n">
-        <v>16.16684</v>
+        <v>16.76208</v>
       </c>
       <c r="E16" t="n">
-        <v>16.93047</v>
+        <v>16.91504</v>
       </c>
       <c r="F16" t="n">
-        <v>41.74739</v>
+        <v>42.31963</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05044</v>
+        <v>0.05155</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8066</v>
+        <v>1.80848</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.99448</v>
+        <v>17.10413</v>
       </c>
       <c r="D17" t="n">
-        <v>16.6171</v>
+        <v>16.59925</v>
       </c>
       <c r="E17" t="n">
-        <v>17.24132</v>
+        <v>16.90025</v>
       </c>
       <c r="F17" t="n">
-        <v>43.38383</v>
+        <v>41.65595</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05111</v>
+        <v>0.05088</v>
       </c>
       <c r="H17" t="n">
-        <v>1.85592</v>
+        <v>1.84429</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.22797</v>
+        <v>16.91094</v>
       </c>
       <c r="D18" t="n">
-        <v>16.34531</v>
+        <v>16.67293</v>
       </c>
       <c r="E18" t="n">
-        <v>16.87885</v>
+        <v>16.80016</v>
       </c>
       <c r="F18" t="n">
-        <v>43.05603</v>
+        <v>43.21368</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05027</v>
+        <v>0.05021</v>
       </c>
       <c r="H18" t="n">
-        <v>1.83289</v>
+        <v>1.84974</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.72948</v>
+        <v>17.19464</v>
       </c>
       <c r="D19" t="n">
-        <v>16.62501</v>
+        <v>16.42913</v>
       </c>
       <c r="E19" t="n">
-        <v>16.70044</v>
+        <v>16.78991</v>
       </c>
       <c r="F19" t="n">
-        <v>42.56641</v>
+        <v>43.52972</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05121</v>
+        <v>0.0522</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84245</v>
+        <v>1.83226</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.75939</v>
+        <v>16.97908</v>
       </c>
       <c r="D20" t="n">
-        <v>16.62842</v>
+        <v>16.33079</v>
       </c>
       <c r="E20" t="n">
-        <v>16.77066</v>
+        <v>16.90421</v>
       </c>
       <c r="F20" t="n">
-        <v>43.31878</v>
+        <v>42.3789</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05096</v>
+        <v>0.05163</v>
       </c>
       <c r="H20" t="n">
-        <v>1.84485</v>
+        <v>1.80787</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.65195</v>
+        <v>15.91125</v>
       </c>
       <c r="D22" t="n">
-        <v>15.4686</v>
+        <v>15.37823</v>
       </c>
       <c r="E22" t="n">
-        <v>15.92253</v>
+        <v>15.88294</v>
       </c>
       <c r="F22" t="n">
-        <v>261.05246</v>
+        <v>254.59266</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.98315</v>
+        <v>16.15505</v>
       </c>
       <c r="D23" t="n">
-        <v>15.77058</v>
+        <v>15.50942</v>
       </c>
       <c r="E23" t="n">
-        <v>15.79182</v>
+        <v>15.54599</v>
       </c>
       <c r="F23" t="n">
-        <v>255.58587</v>
+        <v>253.17839</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.77182</v>
+        <v>15.79946</v>
       </c>
       <c r="D24" t="n">
-        <v>15.74246</v>
+        <v>15.70725</v>
       </c>
       <c r="E24" t="n">
-        <v>16.00599</v>
+        <v>15.7669</v>
       </c>
       <c r="F24" t="n">
-        <v>255.22876</v>
+        <v>257.65769</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.89636</v>
+        <v>15.81105</v>
       </c>
       <c r="D25" t="n">
-        <v>15.74855</v>
+        <v>15.58016</v>
       </c>
       <c r="E25" t="n">
-        <v>15.89975</v>
+        <v>15.73342</v>
       </c>
       <c r="F25" t="n">
-        <v>253.32909</v>
+        <v>256.76835</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.39195</v>
+        <v>15.97943</v>
       </c>
       <c r="D26" t="n">
-        <v>15.7741</v>
+        <v>15.63302</v>
       </c>
       <c r="E26" t="n">
-        <v>15.67232</v>
+        <v>15.95152</v>
       </c>
       <c r="F26" t="n">
-        <v>251.59527</v>
+        <v>255.92616</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.8299</v>
+        <v>15.78012</v>
       </c>
       <c r="D27" t="n">
-        <v>15.69336</v>
+        <v>15.66498</v>
       </c>
       <c r="E27" t="n">
-        <v>15.72984</v>
+        <v>15.67298</v>
       </c>
       <c r="F27" t="n">
-        <v>255.32657</v>
+        <v>251.83745</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>16.25654</v>
+        <v>16.08419</v>
       </c>
       <c r="D28" t="n">
-        <v>15.6104</v>
+        <v>15.5722</v>
       </c>
       <c r="E28" t="n">
-        <v>15.97412</v>
+        <v>15.77913</v>
       </c>
       <c r="F28" t="n">
-        <v>254.08802</v>
+        <v>260.13677</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.71039</v>
+        <v>15.80336</v>
       </c>
       <c r="D29" t="n">
-        <v>15.51197</v>
+        <v>15.57949</v>
       </c>
       <c r="E29" t="n">
-        <v>15.7458</v>
+        <v>15.68367</v>
       </c>
       <c r="F29" t="n">
-        <v>260.36823</v>
+        <v>255.98898</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.62861</v>
+        <v>15.80742</v>
       </c>
       <c r="D30" t="n">
-        <v>15.66018</v>
+        <v>15.52483</v>
       </c>
       <c r="E30" t="n">
-        <v>15.70093</v>
+        <v>15.75888</v>
       </c>
       <c r="F30" t="n">
-        <v>257.15744</v>
+        <v>252.50322</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.89457</v>
+        <v>16.84833</v>
       </c>
       <c r="D32" t="n">
-        <v>16.25049</v>
+        <v>16.02718</v>
       </c>
       <c r="E32" t="n">
-        <v>16.44807</v>
+        <v>16.57132</v>
       </c>
       <c r="F32" t="n">
-        <v>21.83742</v>
+        <v>21.76666</v>
       </c>
       <c r="G32" t="n">
-        <v>34.64541</v>
+        <v>34.14251</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17.2179</v>
+        <v>16.6127</v>
       </c>
       <c r="D33" t="n">
-        <v>16.35475</v>
+        <v>16.04419</v>
       </c>
       <c r="E33" t="n">
-        <v>16.47567</v>
+        <v>16.31191</v>
       </c>
       <c r="F33" t="n">
-        <v>21.52783</v>
+        <v>22.1402</v>
       </c>
       <c r="G33" t="n">
-        <v>34.34865</v>
+        <v>34.08689</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.91751</v>
+        <v>16.89533</v>
       </c>
       <c r="D34" t="n">
-        <v>16.40648</v>
+        <v>16.13595</v>
       </c>
       <c r="E34" t="n">
-        <v>16.46977</v>
+        <v>16.56647</v>
       </c>
       <c r="F34" t="n">
-        <v>21.91905</v>
+        <v>21.9449</v>
       </c>
       <c r="G34" t="n">
-        <v>35.19466</v>
+        <v>33.76728</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.84995</v>
+        <v>16.70638</v>
       </c>
       <c r="D35" t="n">
-        <v>15.99956</v>
+        <v>16.06068</v>
       </c>
       <c r="E35" t="n">
-        <v>16.75558</v>
+        <v>16.60856</v>
       </c>
       <c r="F35" t="n">
-        <v>21.73829</v>
+        <v>22.05914</v>
       </c>
       <c r="G35" t="n">
-        <v>33.53081</v>
+        <v>34.09187</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.98048</v>
+        <v>16.56969</v>
       </c>
       <c r="D36" t="n">
-        <v>16.10133</v>
+        <v>15.86629</v>
       </c>
       <c r="E36" t="n">
-        <v>16.54973</v>
+        <v>16.38118</v>
       </c>
       <c r="F36" t="n">
-        <v>21.89069</v>
+        <v>22.19949</v>
       </c>
       <c r="G36" t="n">
-        <v>34.25547</v>
+        <v>35.24773</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.79459</v>
+        <v>16.88336</v>
       </c>
       <c r="D37" t="n">
-        <v>16.15865</v>
+        <v>15.92841</v>
       </c>
       <c r="E37" t="n">
-        <v>16.39885</v>
+        <v>16.64518</v>
       </c>
       <c r="F37" t="n">
-        <v>21.52288</v>
+        <v>21.95698</v>
       </c>
       <c r="G37" t="n">
-        <v>34.58534</v>
+        <v>34.64979</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.6904</v>
+        <v>17.11864</v>
       </c>
       <c r="D38" t="n">
-        <v>16.2188</v>
+        <v>16.02985</v>
       </c>
       <c r="E38" t="n">
-        <v>16.43728</v>
+        <v>16.24418</v>
       </c>
       <c r="F38" t="n">
-        <v>21.70045</v>
+        <v>21.86832</v>
       </c>
       <c r="G38" t="n">
-        <v>35.21798</v>
+        <v>34.20259</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>17.11808</v>
+        <v>16.58511</v>
       </c>
       <c r="D39" t="n">
-        <v>16.3165</v>
+        <v>15.95934</v>
       </c>
       <c r="E39" t="n">
-        <v>16.19932</v>
+        <v>16.4057</v>
       </c>
       <c r="F39" t="n">
-        <v>21.84417</v>
+        <v>21.50116</v>
       </c>
       <c r="G39" t="n">
-        <v>34.59184</v>
+        <v>34.10395</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.81134</v>
+        <v>16.95294</v>
       </c>
       <c r="D40" t="n">
-        <v>15.82106</v>
+        <v>15.92064</v>
       </c>
       <c r="E40" t="n">
-        <v>16.30732</v>
+        <v>16.69478</v>
       </c>
       <c r="F40" t="n">
-        <v>21.78317</v>
+        <v>21.69077</v>
       </c>
       <c r="G40" t="n">
-        <v>34.34852</v>
+        <v>34.49375</v>
       </c>
     </row>
     <row r="41">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.6117899999999999</v>
+        <v>0.59002</v>
       </c>
       <c r="D42" t="n">
-        <v>1.16433</v>
+        <v>1.11787</v>
       </c>
     </row>
     <row r="43">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.60506</v>
+        <v>0.61199</v>
       </c>
       <c r="D43" t="n">
-        <v>1.10875</v>
+        <v>1.12222</v>
       </c>
     </row>
     <row r="44">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.60263</v>
+        <v>0.61664</v>
       </c>
       <c r="D44" t="n">
-        <v>1.12653</v>
+        <v>1.12163</v>
       </c>
     </row>
     <row r="45">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.60417</v>
+        <v>0.60586</v>
       </c>
       <c r="D45" t="n">
-        <v>1.13046</v>
+        <v>1.10953</v>
       </c>
     </row>
     <row r="46">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.61302</v>
+        <v>0.61638</v>
       </c>
       <c r="D46" t="n">
-        <v>1.13258</v>
+        <v>1.12935</v>
       </c>
     </row>
     <row r="47">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.60353</v>
+        <v>0.61289</v>
       </c>
       <c r="D47" t="n">
-        <v>1.12897</v>
+        <v>1.1222</v>
       </c>
     </row>
     <row r="48">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.6022999999999999</v>
+        <v>0.62566</v>
       </c>
       <c r="D48" t="n">
-        <v>1.0937</v>
+        <v>1.12799</v>
       </c>
     </row>
     <row r="49">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.61231</v>
+        <v>0.60446</v>
       </c>
       <c r="D49" t="n">
-        <v>1.11432</v>
+        <v>1.13024</v>
       </c>
     </row>
     <row r="50">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.60958</v>
+        <v>0.59597</v>
       </c>
       <c r="D50" t="n">
-        <v>1.12129</v>
+        <v>1.13264</v>
       </c>
     </row>
     <row r="51">
@@ -1536,16 +1536,16 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>16.82705</v>
+        <v>16.82786</v>
       </c>
       <c r="D52" t="n">
-        <v>16.43093</v>
+        <v>16.48109</v>
       </c>
       <c r="E52" t="n">
-        <v>16.81489</v>
+        <v>16.67633</v>
       </c>
       <c r="F52" t="n">
-        <v>42.98371</v>
+        <v>42.72577</v>
       </c>
     </row>
     <row r="53">
@@ -1555,16 +1555,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>17.19247</v>
+        <v>16.91594</v>
       </c>
       <c r="D53" t="n">
-        <v>17.02225</v>
+        <v>16.45594</v>
       </c>
       <c r="E53" t="n">
-        <v>16.72399</v>
+        <v>16.67617</v>
       </c>
       <c r="F53" t="n">
-        <v>42.43463</v>
+        <v>42.34306</v>
       </c>
     </row>
     <row r="54">
@@ -1574,16 +1574,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>16.82356</v>
+        <v>16.85925</v>
       </c>
       <c r="D54" t="n">
-        <v>16.73867</v>
+        <v>16.64342</v>
       </c>
       <c r="E54" t="n">
-        <v>16.86238</v>
+        <v>16.76182</v>
       </c>
       <c r="F54" t="n">
-        <v>42.60925</v>
+        <v>42.22011</v>
       </c>
     </row>
     <row r="55">
@@ -1593,16 +1593,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>17.00652</v>
+        <v>16.98075</v>
       </c>
       <c r="D55" t="n">
-        <v>16.21524</v>
+        <v>16.64889</v>
       </c>
       <c r="E55" t="n">
-        <v>17.04058</v>
+        <v>16.95121</v>
       </c>
       <c r="F55" t="n">
-        <v>42.34143</v>
+        <v>42.75664</v>
       </c>
     </row>
     <row r="56">
@@ -1612,16 +1612,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>16.62879</v>
+        <v>17.18832</v>
       </c>
       <c r="D56" t="n">
-        <v>16.71721</v>
+        <v>16.436</v>
       </c>
       <c r="E56" t="n">
-        <v>16.94324</v>
+        <v>16.7998</v>
       </c>
       <c r="F56" t="n">
-        <v>43.98913</v>
+        <v>42.57814</v>
       </c>
     </row>
     <row r="57">
@@ -1631,16 +1631,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>16.94579</v>
+        <v>16.93381</v>
       </c>
       <c r="D57" t="n">
-        <v>16.73373</v>
+        <v>16.52278</v>
       </c>
       <c r="E57" t="n">
-        <v>16.50493</v>
+        <v>16.86875</v>
       </c>
       <c r="F57" t="n">
-        <v>42.45904</v>
+        <v>41.87101</v>
       </c>
     </row>
     <row r="58">
@@ -1650,16 +1650,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>16.77499</v>
+        <v>16.9462</v>
       </c>
       <c r="D58" t="n">
-        <v>16.80881</v>
+        <v>16.59565</v>
       </c>
       <c r="E58" t="n">
-        <v>16.80834</v>
+        <v>16.85553</v>
       </c>
       <c r="F58" t="n">
-        <v>42.72305</v>
+        <v>42.96882</v>
       </c>
     </row>
     <row r="59">
@@ -1669,16 +1669,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>17.23387</v>
+        <v>17.13025</v>
       </c>
       <c r="D59" t="n">
-        <v>16.7196</v>
+        <v>16.40501</v>
       </c>
       <c r="E59" t="n">
-        <v>16.82143</v>
+        <v>16.98271</v>
       </c>
       <c r="F59" t="n">
-        <v>42.40782</v>
+        <v>42.5543</v>
       </c>
     </row>
     <row r="60">
@@ -1688,16 +1688,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>16.84372</v>
+        <v>16.94729</v>
       </c>
       <c r="D60" t="n">
-        <v>16.86699</v>
+        <v>16.68597</v>
       </c>
       <c r="E60" t="n">
-        <v>16.8089</v>
+        <v>16.74836</v>
       </c>
       <c r="F60" t="n">
-        <v>41.87097</v>
+        <v>42.76993</v>
       </c>
     </row>
   </sheetData>
